--- a/output/pdf_financials_xlsx/ARU.xlsx
+++ b/output/pdf_financials_xlsx/ARU.xlsx
@@ -1194,19 +1194,19 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.325832</v>
+        <v>-0.325832</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.633393</v>
+        <v>-1.633393</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.622635</v>
+        <v>-0.622635</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.444149</v>
+        <v>-0.444149</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.518299</v>
+        <v>-0.518299</v>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
@@ -1214,22 +1214,22 @@
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>9.624344000000001</v>
+        <v>-9.624344000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>16.602833</v>
+        <v>-16.602833</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>23.405779</v>
+        <v>-23.405779</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>12.329074</v>
+        <v>-12.329074</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>9.971545000000001</v>
+        <v>-9.971545000000001</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>10.833344</v>
+        <v>-10.833344</v>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.325832</v>
+        <v>-0.325832</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.633393</v>
+        <v>-1.633393</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.622635</v>
+        <v>-0.622635</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.444149</v>
+        <v>-0.444149</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.518299</v>
+        <v>-0.518299</v>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
@@ -1476,22 +1476,22 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>9.624344000000001</v>
+        <v>-9.624344000000001</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>16.602833</v>
+        <v>-16.602833</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>23.405779</v>
+        <v>-23.405779</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>12.329074</v>
+        <v>-12.329074</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>9.971545000000001</v>
+        <v>-9.971545000000001</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>10.833344</v>
+        <v>-10.833344</v>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
@@ -1617,19 +1617,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.325832</v>
+        <v>-0.325832</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.633393</v>
+        <v>-1.633393</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.622635</v>
+        <v>-0.622635</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.444149</v>
+        <v>-0.444149</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.518299</v>
+        <v>-0.518299</v>
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
@@ -1637,22 +1637,22 @@
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>9.624344000000001</v>
+        <v>-9.624344000000001</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>16.602833</v>
+        <v>-16.602833</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>23.405779</v>
+        <v>-23.405779</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>12.329074</v>
+        <v>-12.329074</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>9.971545000000001</v>
+        <v>-9.971545000000001</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>10.833344</v>
+        <v>-10.833344</v>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
@@ -1778,19 +1778,19 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>15.51581</v>
+        <v>-15.51581</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>21.212896</v>
+        <v>-21.212896</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>20.7545</v>
+        <v>-20.7545</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>22.20745</v>
+        <v>-22.20745</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>25.91495</v>
+        <v>-25.91495</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
@@ -1798,22 +1798,22 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>30.076075</v>
+        <v>-30.076075</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>35.325177</v>
+        <v>-35.325177</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>42.555962</v>
+        <v>-42.555962</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>53.60467</v>
+        <v>-53.60467</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>66.476967</v>
+        <v>-66.476967</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>83.333415</v>
+        <v>-83.333415</v>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
@@ -1833,19 +1833,19 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.325832</v>
+        <v>-0.325832</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.633393</v>
+        <v>-1.633393</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.622635</v>
+        <v>-0.622635</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.444149</v>
+        <v>-0.444149</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.518299</v>
+        <v>-0.518299</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -1853,22 +1853,22 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>9.624344000000001</v>
+        <v>-9.624344000000001</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>16.602833</v>
+        <v>-16.602833</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>23.405779</v>
+        <v>-23.405779</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>12.329074</v>
+        <v>-12.329074</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>9.971545000000001</v>
+        <v>-9.971545000000001</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>10.833344</v>
+        <v>-10.833344</v>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
@@ -1941,19 +1941,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.332297</v>
+        <v>-0.319367</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.636441</v>
+        <v>-1.630345</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.622635</v>
+        <v>-0.622635</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.444149</v>
+        <v>-0.444149</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.518299</v>
+        <v>-0.518299</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -1961,22 +1961,22 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>9.624344000000001</v>
+        <v>-9.624344000000001</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>16.602833</v>
+        <v>-16.602833</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>23.405779</v>
+        <v>-23.405779</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>12.329074</v>
+        <v>-12.329074</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>9.971545000000001</v>
+        <v>-9.971545000000001</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>10.833344</v>
+        <v>-10.833344</v>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
@@ -2073,19 +2073,19 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
@@ -2093,22 +2093,22 @@
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
@@ -5703,22 +5703,22 @@
         </is>
       </c>
       <c r="I99" s="3" t="n">
-        <v>9.624344000000001</v>
+        <v>-9.624344000000001</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>16.602833</v>
+        <v>-16.602833</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>23.405779</v>
+        <v>-23.405779</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>12.329074</v>
+        <v>-12.329074</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>9.971545000000001</v>
+        <v>-9.971545000000001</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>10.833344</v>
+        <v>-10.833344</v>
       </c>
       <c r="O99" s="1" t="inlineStr">
         <is>
@@ -36367,10 +36367,10 @@
         </is>
       </c>
       <c r="P333" s="5" t="n">
-        <v>9.971545000000001</v>
+        <v>-9.971545000000001</v>
       </c>
       <c r="Q333" s="5" t="n">
-        <v>10.833344</v>
+        <v>-10.833344</v>
       </c>
       <c r="R333" t="inlineStr">
         <is>
@@ -37560,10 +37560,10 @@
         </is>
       </c>
       <c r="O347" s="5" t="n">
-        <v>12.329074</v>
+        <v>-12.329074</v>
       </c>
       <c r="P347" s="5" t="n">
-        <v>9.971545000000001</v>
+        <v>-9.971545000000001</v>
       </c>
       <c r="Q347" t="inlineStr">
         <is>
@@ -38075,10 +38075,10 @@
         </is>
       </c>
       <c r="N353" s="5" t="n">
-        <v>23.405779</v>
+        <v>-23.405779</v>
       </c>
       <c r="O353" s="5" t="n">
-        <v>12.329074</v>
+        <v>-12.329074</v>
       </c>
       <c r="P353" t="inlineStr">
         <is>
@@ -39793,10 +39793,10 @@
         </is>
       </c>
       <c r="L373" s="5" t="n">
-        <v>9.624344000000001</v>
+        <v>-9.624344000000001</v>
       </c>
       <c r="M373" s="5" t="n">
-        <v>16.602833</v>
+        <v>-16.602833</v>
       </c>
       <c r="N373" t="inlineStr">
         <is>
@@ -44351,19 +44351,19 @@
         </is>
       </c>
       <c r="F426" s="5" t="n">
-        <v>0.325832</v>
+        <v>-0.325832</v>
       </c>
       <c r="G426" s="5" t="n">
-        <v>1.633393</v>
+        <v>-1.633393</v>
       </c>
       <c r="H426" s="5" t="n">
-        <v>0.622635</v>
+        <v>-0.622635</v>
       </c>
       <c r="I426" s="5" t="n">
-        <v>0.444149</v>
+        <v>-0.444149</v>
       </c>
       <c r="J426" s="5" t="n">
-        <v>0.518299</v>
+        <v>-0.518299</v>
       </c>
       <c r="K426" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ARU.xlsx
+++ b/output/pdf_financials_xlsx/ARU.xlsx
@@ -874,40 +874,40 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.048882</v>
+        <v>0.235304</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.214022</v>
+        <v>1.477397</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.242858</v>
+        <v>0.624783</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.227409</v>
+        <v>0.444258</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.14392</v>
+        <v>0.512791</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.853058</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.567708</v>
+        <v>9.316663</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>2.186637</v>
+        <v>16.200347</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>2.84728</v>
+        <v>22.828285</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>2.978708</v>
+        <v>10.904112</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1.896188</v>
+        <v>8.408639000000001</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>2.3827</v>
+        <v>8.703302000000001</v>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.048882</v>
+        <v>-0.235304</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.214022</v>
+        <v>-1.477397</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.242858</v>
+        <v>-0.624783</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.227409</v>
+        <v>-0.444258</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.14392</v>
+        <v>-0.512791</v>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
@@ -947,22 +947,22 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-1.567708</v>
+        <v>-9.316663</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-2.186637</v>
+        <v>-16.200347</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-2.84728</v>
+        <v>-22.828285</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-2.978708</v>
+        <v>-10.904112</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-1.896188</v>
+        <v>-8.408639000000001</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-2.3827</v>
+        <v>-8.703302000000001</v>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
@@ -985,13 +985,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005013</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002363</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000119</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1000,22 +1000,22 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.009127</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.009093</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.006144</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.013333</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003857</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.039796</v>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
@@ -1836,13 +1836,13 @@
         <v>-0.325832</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.633393</v>
+        <v>-1.62838</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.622635</v>
+        <v>-0.620272</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.444149</v>
+        <v>-0.44403</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.518299</v>
@@ -1853,22 +1853,22 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-9.624344000000001</v>
+        <v>-9.615216999999999</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-16.602833</v>
+        <v>-16.59374</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-23.405779</v>
+        <v>-23.399635</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-12.329074</v>
+        <v>-12.315741</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-9.971545000000001</v>
+        <v>-9.967688000000001</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-10.833344</v>
+        <v>-10.793548</v>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
@@ -1944,13 +1944,13 @@
         <v>-0.319367</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.630345</v>
+        <v>-1.625332</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.622635</v>
+        <v>-0.620272</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.444149</v>
+        <v>-0.44403</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.518299</v>
@@ -1961,22 +1961,22 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-9.624344000000001</v>
+        <v>-9.615216999999999</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-16.602833</v>
+        <v>-16.59374</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-23.405779</v>
+        <v>-23.399635</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-12.329074</v>
+        <v>-12.315741</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-9.971545000000001</v>
+        <v>-9.967688000000001</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-10.833344</v>
+        <v>-10.793548</v>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
@@ -2212,40 +2212,40 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.312831</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.892486</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.21134</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.007753</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.003942</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.671346</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.817021</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>5.229341</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>4.522657</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.473768</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.325262</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.593204</v>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
@@ -2318,40 +2318,40 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.312831</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.892486</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.21134</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.007753</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.003942</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.671346</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.817021</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>5.229341</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>4.522657</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.473768</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.325262</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.593204</v>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
@@ -2954,40 +2954,40 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.347771</v>
+        <v>0.03494</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.897746</v>
+        <v>0.00526</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.214197</v>
+        <v>0.002857</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.006454</v>
+        <v>0.002512</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.736228</v>
+        <v>0.064882</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.170387</v>
+        <v>0.353366</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>6.174264</v>
+        <v>0.944923</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>4.580227</v>
+        <v>0.05757</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.905207</v>
+        <v>0.431439</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.389354</v>
+        <v>0.064092</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.751834</v>
+        <v>0.15863</v>
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>0</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.018175</v>
       </c>
       <c r="M124" s="3" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
         <v>0</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.018175</v>
       </c>
       <c r="M125" s="3" t="n">
         <v>0</v>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -18336,7 +18336,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -24932,7 +24932,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -35880,7 +35884,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -36052,7 +36056,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -37854,7 +37858,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -39146,7 +39150,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -39496,7 +39500,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -41414,7 +41418,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -44090,7 +44094,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -44172,7 +44176,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -45358,7 +45362,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">

--- a/output/pdf_financials_xlsx/ARU.xlsx
+++ b/output/pdf_financials_xlsx/ARU.xlsx
@@ -715,19 +715,19 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.037767</v>
+        <v>0.09776700000000001</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.166615</v>
+        <v>0.272115</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.202611</v>
+        <v>0.330411</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.186086</v>
+        <v>0.313886</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.105444</v>
+        <v>0.234098</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.853058</v>
@@ -21336,7 +21336,11 @@
           <t>Shares issued for private placement (note 12)</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -23228,7 +23232,11 @@
           <t>Shares issued for private placement (note 11)</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -42468,7 +42476,11 @@
           <t>Directors’ fees 63,375</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E404" t="inlineStr">
         <is>
           <t>-</t>
@@ -43764,7 +43776,11 @@
           <t>Management and directors’ fees (note 10)</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -45192,7 +45208,11 @@
           <t>Management and directors’ fees (Note 9)</t>
         </is>
       </c>
-      <c r="D436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr">
         <is>
           <t>-</t>
@@ -45700,7 +45720,11 @@
           <t>Management and directors’ fees (Note 11)</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E442" t="inlineStr">
         <is>
           <t>-</t>
